--- a/public/templates/mau-nhap-lieu.xlsx
+++ b/public/templates/mau-nhap-lieu.xlsx
@@ -405,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,7 +419,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2. Sản phẩm/Nguyên liệu/Topping: trùng tên với dữ liệu đã có sẽ CẬP NHẬT giá (Nguyên liệu cập nhật cả đơn vị) — không tạo trùng.</v>
+        <v>2. Nhập = GHI ĐÈ TOÀN BỘ: sheet nào có trong file thì phần đó của địa chỉ được thay hoàn toàn theo file. Món, danh mục, topping, tùy chọn, công thức không có trong file sẽ bị XOÁ. Sheet nào xoá khỏi file thì phần đó giữ nguyên. Nguyên liệu không bao giờ bị xoá, chỉ thêm/cập nhật giá vốn và đơn vị.</v>
       </c>
     </row>
     <row r="4">
@@ -444,19 +444,24 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>7. Sheet Topping áp dụng món: ghi đè TOÀN BỘ danh sách món của mỗi topping trong file — món cũ không có trong file sẽ bị gỡ liên kết.</v>
+        <v>7. Sheet Topping áp dụng món: toàn bộ liên kết topping-món được thay theo file.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>8. Cột Danh mục (sheet Sản phẩm, tuỳ chọn): điền tên danh mục để nhóm món và xếp thứ tự menu đúng theo thứ tự dòng trong file. Danh mục chưa có sẽ được tạo mới. Để trống toàn bộ cột = không đổi thứ tự menu hiện tại.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -465,6 +470,9 @@
       <c r="B1" t="str">
         <v>Giá bán</v>
       </c>
+      <c r="C1" t="str">
+        <v>Danh mục</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -473,6 +481,9 @@
       <c r="B2">
         <v>16000</v>
       </c>
+      <c r="C2" t="str">
+        <v>Cà phê</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -481,10 +492,13 @@
       <c r="B3">
         <v>18000</v>
       </c>
+      <c r="C3" t="str">
+        <v>Cà phê</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/templates/mau-nhap-lieu.xlsx
+++ b/public/templates/mau-nhap-lieu.xlsx
@@ -12,6 +12,8 @@
     <sheet name="Topping áp dụng món" sheetId="7" r:id="rId7"/>
     <sheet name="Tùy chọn thêm" sheetId="8" r:id="rId8"/>
     <sheet name="Công thức tùy chọn" sheetId="9" r:id="rId9"/>
+    <sheet name="Giảm giá" sheetId="10" r:id="rId10"/>
+    <sheet name="Giảm giá áp dụng món" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -405,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,7 +421,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2. Nhập = GHI ĐÈ TOÀN BỘ: sheet nào có trong file thì phần đó của địa chỉ được thay hoàn toàn theo file. Món, danh mục, topping, tùy chọn, công thức không có trong file sẽ bị XOÁ. Sheet nào xoá khỏi file thì phần đó giữ nguyên. Nguyên liệu không bao giờ bị xoá, chỉ thêm/cập nhật giá vốn và đơn vị.</v>
+        <v>2. Nhập = GHI ĐÈ TOÀN BỘ: sheet nào có trong file thì phần đó của địa chỉ được thay hoàn toàn theo file. Món, danh mục, topping, tùy chọn, công thức, chương trình giảm giá không có trong file sẽ bị XOÁ. Sheet nào xoá khỏi file thì phần đó giữ nguyên. Nguyên liệu không bao giờ bị xoá, chỉ thêm/cập nhật.</v>
       </c>
     </row>
     <row r="4">
@@ -452,9 +454,113 @@
         <v>8. Cột Danh mục (sheet Sản phẩm, tuỳ chọn): điền tên danh mục để nhóm món và xếp thứ tự menu đúng theo thứ tự dòng trong file. Danh mục chưa có sẽ được tạo mới. Để trống toàn bộ cột = không đổi thứ tự menu hiện tại.</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>9. Sheet Nguyên liệu, cột Nhóm (tuỳ chọn): tên nhóm nguyên liệu trong tab Nguyên liệu/Bao bì; nhóm chưa có sẽ được tạo theo thứ tự xuất hiện. Cột Nhóm có trong file mà để trống = bỏ khỏi nhóm.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>10. Sheet Nguyên liệu, cột Quy cách / Đơn vị quy cách: 1 [đơn vị quy cách] = [Quy cách] [đơn vị gốc], vd 1 bịch = 500 g. Quy cách 2: 1 [đơn vị quy cách 2] = [Quy cách 2] [đơn vị quy cách], vd 1 thùng = 20 bịch. Tồn kho tối thiểu / Tồn quầy tối thiểu tính theo đơn vị gốc. Cột nào có trong file thì ô trống = xoá giá trị; xoá hẳn cột = giữ nguyên.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>11. Sheet Giảm giá: Kiểu là "Đồng giá" (Giá trị = giá bán mới), "Giảm %" (0-100) hoặc "Giảm tiền" (số tiền giảm). Thứ áp dụng: T2..T7, CN cách nhau dấu phẩy, để trống = mọi ngày. Từ ngày / Đến ngày: YYYY-MM-DD hoặc ô ngày của Excel, để trống = không giới hạn. Bật: "có" để chạy ngay, để trống = tắt.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>12. Sheet Giảm giá áp dụng món: mỗi dòng gắn 1 món vào 1 chương trình; toàn bộ món của các chương trình trong sheet Giảm giá được thay theo file.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tên chương trình</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Kiểu</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Giá trị</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Thứ áp dụng</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Từ ngày</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Đến ngày</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Bật</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Happy hour thứ 2</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Giảm %</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2" t="str">
+        <v>T2</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tên chương trình</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Tên món</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Happy hour thứ 2</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cà Phê Sữa</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -505,7 +611,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:K4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -520,6 +626,27 @@
       <c r="D1" t="str">
         <v>Loại</v>
       </c>
+      <c r="E1" t="str">
+        <v>Nhóm</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Quy cách</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Đơn vị quy cách</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Quy cách 2</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Đơn vị quy cách 2</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Tồn kho tối thiểu</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Tồn quầy tối thiểu</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -534,6 +661,27 @@
       <c r="D2" t="str">
         <v>chính</v>
       </c>
+      <c r="E2" t="str">
+        <v>Cà phê &amp; sữa</v>
+      </c>
+      <c r="F2">
+        <v>500</v>
+      </c>
+      <c r="G2" t="str">
+        <v>bịch</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2" t="str">
+        <v>thùng</v>
+      </c>
+      <c r="J2">
+        <v>1000</v>
+      </c>
+      <c r="K2">
+        <v>200</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -548,6 +696,27 @@
       <c r="D3" t="str">
         <v>chính</v>
       </c>
+      <c r="E3" t="str">
+        <v>Cà phê &amp; sữa</v>
+      </c>
+      <c r="F3">
+        <v>380</v>
+      </c>
+      <c r="G3" t="str">
+        <v>lon</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3">
+        <v>760</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -562,10 +731,31 @@
       <c r="D4" t="str">
         <v>bao bì</v>
       </c>
+      <c r="E4" t="str">
+        <v>Ly &amp; nắp</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>
